--- a/artfynd/A 22067-2024 artfynd.xlsx
+++ b/artfynd/A 22067-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128945338</v>
       </c>
       <c r="B2" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128945349</v>
       </c>
       <c r="B3" t="n">
-        <v>80226</v>
+        <v>80230</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22067-2024 artfynd.xlsx
+++ b/artfynd/A 22067-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128945338</v>
       </c>
       <c r="B2" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128945349</v>
       </c>
       <c r="B3" t="n">
-        <v>80230</v>
+        <v>80135</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22067-2024 artfynd.xlsx
+++ b/artfynd/A 22067-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128945338</v>
       </c>
       <c r="B2" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128945349</v>
       </c>
       <c r="B3" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22067-2024 artfynd.xlsx
+++ b/artfynd/A 22067-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128945338</v>
       </c>
       <c r="B2" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128945349</v>
       </c>
       <c r="B3" t="n">
-        <v>80141</v>
+        <v>80145</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22067-2024 artfynd.xlsx
+++ b/artfynd/A 22067-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128945338</v>
       </c>
       <c r="B2" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128945349</v>
       </c>
       <c r="B3" t="n">
-        <v>80145</v>
+        <v>80147</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22067-2024 artfynd.xlsx
+++ b/artfynd/A 22067-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128945338</v>
       </c>
       <c r="B2" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128945349</v>
       </c>
       <c r="B3" t="n">
-        <v>80147</v>
+        <v>80149</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22067-2024 artfynd.xlsx
+++ b/artfynd/A 22067-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128945338</v>
       </c>
       <c r="B2" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128945349</v>
       </c>
       <c r="B3" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22067-2024 artfynd.xlsx
+++ b/artfynd/A 22067-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128945338</v>
+        <v>128945452</v>
       </c>
       <c r="B2" t="n">
-        <v>79044</v>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Peslaskorp, Peslaskorp, Dlr</t>
+          <t>Hästtjärnarna, Hästtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>476637</v>
+        <v>476451</v>
       </c>
       <c r="R2" t="n">
-        <v>6846993</v>
+        <v>6846886</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,12 +760,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -775,7 +775,7 @@
         <v>128945349</v>
       </c>
       <c r="B3" t="n">
-        <v>80150</v>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -866,6 +866,685 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128945038</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Peslaskorp, Peslaskorp, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>476663</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6846823</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128945338</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Peslaskorp, Peslaskorp, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>476637</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6846993</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128945423</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hästtjärnarna, Hästtjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>476452</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6846888</v>
+      </c>
+      <c r="S6" t="n">
+        <v>20</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128945490</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Peslaskorp, Peslaskorp, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>476652</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6847012</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128945650</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Peslaskorp, Peslaskorp, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>476460</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6846879</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128945685</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Peslaskorp, Peslaskorp, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>476459</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6846881</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128945403</v>
+      </c>
+      <c r="B10" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Peslaskorp, Peslaskorp, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>476656</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6847005</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22067-2024 artfynd.xlsx
+++ b/artfynd/A 22067-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128945452</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128945349</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128945038</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128945338</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128945423</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128945490</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128945650</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128945685</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,8 +1590,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128945403</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>